--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C257"/>
+  <dimension ref="A1:C258"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -3236,1172 +3236,1185 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
+      <c r="A168" s="2" t="n">
         <v>300400002</v>
       </c>
-      <c r="B168" t="n">
-        <v>0</v>
-      </c>
-      <c r="C168" t="inlineStr">
+      <c r="B168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
+      <c r="A169" s="2" t="n">
         <v>300400003</v>
       </c>
-      <c r="B169" t="n">
-        <v>0</v>
-      </c>
-      <c r="C169" t="inlineStr">
+      <c r="B169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
         <is>
           <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
+      <c r="A170" s="2" t="n">
         <v>300400004</v>
       </c>
-      <c r="B170" t="n">
-        <v>0</v>
-      </c>
-      <c r="C170" t="inlineStr">
+      <c r="B170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
         <is>
           <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
+      <c r="A171" s="2" t="n">
         <v>300400005</v>
       </c>
-      <c r="B171" t="n">
-        <v>0</v>
-      </c>
-      <c r="C171" t="inlineStr">
+      <c r="B171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
         <is>
           <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
+      <c r="A172" s="2" t="n">
         <v>300400101</v>
       </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
-      <c r="C172" t="inlineStr">
+      <c r="B172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
         <is>
           <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="n">
+      <c r="A173" s="2" t="n">
         <v>300400102</v>
       </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" t="inlineStr">
+      <c r="B173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
         <is>
           <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
+      <c r="A174" s="2" t="n">
         <v>300400201</v>
       </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" t="inlineStr">
+      <c r="B174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
         <is>
           <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
+      <c r="A175" s="2" t="n">
         <v>300400301</v>
       </c>
-      <c r="B175" t="n">
-        <v>0</v>
-      </c>
-      <c r="C175" t="inlineStr">
+      <c r="B175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
         <is>
           <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
+      <c r="A176" s="2" t="n">
         <v>300410011</v>
       </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
-      <c r="C176" t="inlineStr">
+      <c r="B176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
         <is>
           <t>孕育战之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="n">
+      <c r="A177" s="2" t="n">
         <v>300410012</v>
       </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
-      <c r="C177" t="inlineStr">
+      <c r="B177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
         <is>
           <t>孕育战之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
+      <c r="A178" s="2" t="n">
         <v>300410013</v>
       </c>
-      <c r="B178" t="n">
-        <v>0</v>
-      </c>
-      <c r="C178" t="inlineStr">
+      <c r="B178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
         <is>
           <t>孕育战之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="n">
+      <c r="A179" s="2" t="n">
         <v>300410021</v>
       </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
-      <c r="C179" t="inlineStr">
+      <c r="B179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>孕育愈之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
+      <c r="A180" s="2" t="n">
         <v>300410022</v>
       </c>
-      <c r="B180" t="n">
-        <v>0</v>
-      </c>
-      <c r="C180" t="inlineStr">
+      <c r="B180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
         <is>
           <t>孕育愈之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="n">
+      <c r="A181" s="2" t="n">
         <v>300410023</v>
       </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
-      <c r="C181" t="inlineStr">
+      <c r="B181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
         <is>
           <t>孕育愈之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
+      <c r="A182" s="2" t="n">
         <v>300410031</v>
       </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
-      <c r="C182" t="inlineStr">
+      <c r="B182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
         <is>
           <t>孕育惑之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
+      <c r="A183" s="2" t="n">
         <v>300410032</v>
       </c>
-      <c r="B183" t="n">
-        <v>0</v>
-      </c>
-      <c r="C183" t="inlineStr">
+      <c r="B183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
         <is>
           <t>孕育惑之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
+      <c r="A184" s="2" t="n">
         <v>300410033</v>
       </c>
-      <c r="B184" t="n">
-        <v>0</v>
-      </c>
-      <c r="C184" t="inlineStr">
+      <c r="B184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
         <is>
           <t>孕育惑之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
+      <c r="A185" s="2" t="n">
         <v>300410041</v>
       </c>
-      <c r="B185" t="n">
-        <v>0</v>
-      </c>
-      <c r="C185" t="inlineStr">
+      <c r="B185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
         <is>
           <t>孕育奥之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
+      <c r="A186" s="2" t="n">
         <v>300410042</v>
       </c>
-      <c r="B186" t="n">
-        <v>0</v>
-      </c>
-      <c r="C186" t="inlineStr">
+      <c r="B186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
         <is>
           <t>孕育奥之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
+      <c r="A187" s="2" t="n">
         <v>300410043</v>
       </c>
-      <c r="B187" t="n">
-        <v>0</v>
-      </c>
-      <c r="C187" t="inlineStr">
+      <c r="B187" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
         <is>
           <t>孕育奥之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
+      <c r="A188" s="2" t="n">
         <v>300410051</v>
       </c>
-      <c r="B188" t="n">
-        <v>0</v>
-      </c>
-      <c r="C188" t="inlineStr">
+      <c r="B188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
         <is>
           <t>孕育盾之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="n">
+      <c r="A189" s="2" t="n">
         <v>300410052</v>
       </c>
-      <c r="B189" t="n">
-        <v>0</v>
-      </c>
-      <c r="C189" t="inlineStr">
+      <c r="B189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
         <is>
           <t>孕育盾之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="n">
+      <c r="A190" s="2" t="n">
         <v>300410053</v>
       </c>
-      <c r="B190" t="n">
-        <v>0</v>
-      </c>
-      <c r="C190" t="inlineStr">
+      <c r="B190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
         <is>
           <t>孕育盾之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="n">
+      <c r="A191" s="2" t="n">
         <v>300500000</v>
       </c>
-      <c r="B191" t="n">
-        <v>0</v>
-      </c>
-      <c r="C191" t="inlineStr">
+      <c r="B191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
         <is>
           <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
+      <c r="A192" s="2" t="n">
         <v>300500001</v>
       </c>
-      <c r="B192" t="n">
-        <v>0</v>
-      </c>
-      <c r="C192" t="inlineStr">
+      <c r="B192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
         <is>
           <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="n">
+      <c r="A193" s="2" t="n">
         <v>300500002</v>
       </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
-      <c r="C193" t="inlineStr">
+      <c r="B193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
+      <c r="A194" s="2" t="n">
         <v>300500003</v>
       </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
-      <c r="C194" t="inlineStr">
+      <c r="B194" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
         <is>
           <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="n">
+      <c r="A195" s="2" t="n">
         <v>300500004</v>
       </c>
-      <c r="B195" t="n">
-        <v>0</v>
-      </c>
-      <c r="C195" t="inlineStr">
+      <c r="B195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="n">
+      <c r="A196" s="2" t="n">
         <v>300500101</v>
       </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
-      <c r="C196" t="inlineStr">
+      <c r="B196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="n">
+      <c r="A197" s="2" t="n">
         <v>300500102</v>
       </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
-      <c r="C197" t="inlineStr">
+      <c r="B197" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="n">
+      <c r="A198" s="2" t="n">
         <v>300500201</v>
       </c>
-      <c r="B198" t="n">
-        <v>0</v>
-      </c>
-      <c r="C198" t="inlineStr">
+      <c r="B198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
         <is>
           <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="n">
+      <c r="A199" s="2" t="n">
         <v>300500301</v>
       </c>
-      <c r="B199" t="n">
-        <v>0</v>
-      </c>
-      <c r="C199" t="inlineStr">
+      <c r="B199" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
+      <c r="A200" s="2" t="n">
         <v>300510011</v>
       </c>
-      <c r="B200" t="n">
-        <v>0</v>
-      </c>
-      <c r="C200" t="inlineStr">
+      <c r="B200" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人战士x1</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="n">
+      <c r="A201" s="2" t="n">
         <v>300510012</v>
       </c>
-      <c r="B201" t="n">
-        <v>0</v>
-      </c>
-      <c r="C201" t="inlineStr">
+      <c r="B201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人战士x5</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
+      <c r="A202" s="2" t="n">
         <v>300510013</v>
       </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
-      <c r="C202" t="inlineStr">
+      <c r="B202" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人战士x10</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
+      <c r="A203" s="2" t="n">
         <v>300510021</v>
       </c>
-      <c r="B203" t="n">
-        <v>0</v>
-      </c>
-      <c r="C203" t="inlineStr">
+      <c r="B203" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人投手x1</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
+      <c r="A204" s="2" t="n">
         <v>300510022</v>
       </c>
-      <c r="B204" t="n">
-        <v>0</v>
-      </c>
-      <c r="C204" t="inlineStr">
+      <c r="B204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人投手x5</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
+      <c r="A205" s="2" t="n">
         <v>300510023</v>
       </c>
-      <c r="B205" t="n">
-        <v>0</v>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B205" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人投手x10</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
+      <c r="A206" s="2" t="n">
         <v>300510031</v>
       </c>
-      <c r="B206" t="n">
-        <v>0</v>
-      </c>
-      <c r="C206" t="inlineStr">
+      <c r="B206" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
+      <c r="A207" s="2" t="n">
         <v>300510032</v>
       </c>
-      <c r="B207" t="n">
-        <v>0</v>
-      </c>
-      <c r="C207" t="inlineStr">
+      <c r="B207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
+      <c r="A208" s="2" t="n">
         <v>300510033</v>
       </c>
-      <c r="B208" t="n">
-        <v>0</v>
-      </c>
-      <c r="C208" t="inlineStr">
+      <c r="B208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
+      <c r="A209" s="2" t="n">
         <v>300510041</v>
       </c>
-      <c r="B209" t="n">
-        <v>0</v>
-      </c>
-      <c r="C209" t="inlineStr">
+      <c r="B209" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
+      <c r="A210" s="2" t="n">
         <v>300510042</v>
       </c>
-      <c r="B210" t="n">
-        <v>0</v>
-      </c>
-      <c r="C210" t="inlineStr">
+      <c r="B210" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="n">
+      <c r="A211" s="2" t="n">
         <v>300510043</v>
       </c>
-      <c r="B211" t="n">
-        <v>0</v>
-      </c>
-      <c r="C211" t="inlineStr">
+      <c r="B211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
         <is>
           <t>孕育牛头人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
+      <c r="A212" s="2" t="n">
         <v>300600000</v>
       </c>
-      <c r="B212" t="n">
-        <v>0</v>
-      </c>
-      <c r="C212" t="inlineStr">
+      <c r="B212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
         <is>
           <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
+      <c r="A213" s="2" t="n">
         <v>300600001</v>
       </c>
-      <c r="B213" t="n">
-        <v>0</v>
-      </c>
-      <c r="C213" t="inlineStr">
+      <c r="B213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
+      <c r="A214" s="2" t="n">
         <v>300600002</v>
       </c>
-      <c r="B214" t="n">
-        <v>0</v>
-      </c>
-      <c r="C214" t="inlineStr">
+      <c r="B214" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
         <is>
           <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="n">
+      <c r="A215" s="2" t="n">
         <v>300600003</v>
       </c>
-      <c r="B215" t="n">
-        <v>0</v>
-      </c>
-      <c r="C215" t="inlineStr">
+      <c r="B215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
         <is>
           <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="n">
+      <c r="A216" s="2" t="n">
         <v>300600004</v>
       </c>
-      <c r="B216" t="n">
-        <v>0</v>
-      </c>
-      <c r="C216" t="inlineStr">
+      <c r="B216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
         <is>
           <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
+      <c r="A217" s="2" t="n">
         <v>300600005</v>
       </c>
-      <c r="B217" t="n">
-        <v>0</v>
-      </c>
-      <c r="C217" t="inlineStr">
+      <c r="B217" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
         <is>
           <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="n">
+      <c r="A218" s="2" t="n">
         <v>300600101</v>
       </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
-      <c r="C218" t="inlineStr">
+      <c r="B218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
         <is>
           <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="n">
+      <c r="A219" s="2" t="n">
         <v>300600102</v>
       </c>
-      <c r="B219" t="n">
-        <v>0</v>
-      </c>
-      <c r="C219" t="inlineStr">
+      <c r="B219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
         <is>
           <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="n">
+      <c r="A220" s="2" t="n">
         <v>300600201</v>
       </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
-      <c r="C220" t="inlineStr">
+      <c r="B220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
         <is>
           <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="n">
+      <c r="A221" s="2" t="n">
         <v>300600301</v>
       </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
-      <c r="C221" t="inlineStr">
+      <c r="B221" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="n">
+      <c r="A222" s="2" t="n">
         <v>300610011</v>
       </c>
-      <c r="B222" t="n">
-        <v>0</v>
-      </c>
-      <c r="C222" t="inlineStr">
+      <c r="B222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林刺客x1</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="n">
+      <c r="A223" s="2" t="n">
         <v>300610012</v>
       </c>
-      <c r="B223" t="n">
-        <v>0</v>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林刺客x5</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="n">
+      <c r="A224" s="2" t="n">
         <v>300610013</v>
       </c>
-      <c r="B224" t="n">
-        <v>0</v>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林刺客x10</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="n">
+      <c r="A225" s="2" t="n">
         <v>300610021</v>
       </c>
-      <c r="B225" t="n">
-        <v>0</v>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="n">
+      <c r="A226" s="2" t="n">
         <v>300610022</v>
       </c>
-      <c r="B226" t="n">
-        <v>0</v>
-      </c>
-      <c r="C226" t="inlineStr">
+      <c r="B226" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
+      <c r="A227" s="2" t="n">
         <v>300610023</v>
       </c>
-      <c r="B227" t="n">
-        <v>0</v>
-      </c>
-      <c r="C227" t="inlineStr">
+      <c r="B227" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="n">
+      <c r="A228" s="2" t="n">
         <v>300610031</v>
       </c>
-      <c r="B228" t="n">
-        <v>0</v>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="B228" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林敢死队x1</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="n">
+      <c r="A229" s="2" t="n">
         <v>300610032</v>
       </c>
-      <c r="B229" t="n">
-        <v>0</v>
-      </c>
-      <c r="C229" t="inlineStr">
+      <c r="B229" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林敢死队x5</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="n">
+      <c r="A230" s="2" t="n">
         <v>300610033</v>
       </c>
-      <c r="B230" t="n">
-        <v>0</v>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="B230" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林敢死队x10</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
+      <c r="A231" s="2" t="n">
         <v>300610041</v>
       </c>
-      <c r="B231" t="n">
-        <v>0</v>
-      </c>
-      <c r="C231" t="inlineStr">
+      <c r="B231" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
+      <c r="A232" s="2" t="n">
         <v>300610042</v>
       </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
-      <c r="C232" t="inlineStr">
+      <c r="B232" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
+      <c r="A233" s="2" t="n">
         <v>300610043</v>
       </c>
-      <c r="B233" t="n">
-        <v>0</v>
-      </c>
-      <c r="C233" t="inlineStr">
+      <c r="B233" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
+      <c r="A234" s="2" t="n">
         <v>300610051</v>
       </c>
-      <c r="B234" t="n">
-        <v>0</v>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
+      <c r="A235" s="2" t="n">
         <v>300610052</v>
       </c>
-      <c r="B235" t="n">
-        <v>0</v>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="n">
+      <c r="A236" s="2" t="n">
         <v>300610053</v>
       </c>
-      <c r="B236" t="n">
-        <v>0</v>
-      </c>
-      <c r="C236" t="inlineStr">
+      <c r="B236" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
         <is>
           <t>孕育哥布林魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="n">
+      <c r="A237" s="2" t="n">
         <v>300700000</v>
       </c>
-      <c r="B237" t="n">
-        <v>0</v>
-      </c>
-      <c r="C237" t="inlineStr">
+      <c r="B237" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
         <is>
           <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="n">
+      <c r="A238" s="2" t="n">
         <v>300700001</v>
       </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
-      <c r="C238" t="inlineStr">
+      <c r="B238" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
         <is>
           <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="n">
+      <c r="A239" s="2" t="n">
         <v>300700002</v>
       </c>
-      <c r="B239" t="n">
-        <v>0</v>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
         <is>
           <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="n">
+      <c r="A240" s="2" t="n">
         <v>300700003</v>
       </c>
-      <c r="B240" t="n">
-        <v>0</v>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B240" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
         <is>
           <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="n">
+      <c r="A241" s="2" t="n">
         <v>300700004</v>
       </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B241" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
         <is>
           <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="n">
+      <c r="A242" s="2" t="n">
         <v>300700101</v>
       </c>
-      <c r="B242" t="n">
-        <v>0</v>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B242" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="n">
+      <c r="A243" s="2" t="n">
         <v>300700102</v>
       </c>
-      <c r="B243" t="n">
-        <v>0</v>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B243" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
         <is>
           <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="n">
+      <c r="A244" s="2" t="n">
         <v>300700201</v>
       </c>
-      <c r="B244" t="n">
-        <v>0</v>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B244" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
         <is>
           <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="n">
+      <c r="A245" s="2" t="n">
         <v>300700301</v>
       </c>
-      <c r="B245" t="n">
-        <v>0</v>
-      </c>
-      <c r="C245" t="inlineStr">
+      <c r="B245" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
         <is>
           <t>奖励-可获取兽人装备</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="n">
+      <c r="A246" s="2" t="n">
         <v>300710011</v>
       </c>
-      <c r="B246" t="n">
-        <v>0</v>
-      </c>
-      <c r="C246" t="inlineStr">
+      <c r="B246" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>孕育兽人战士x1</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="n">
+      <c r="A247" s="2" t="n">
         <v>300710012</v>
       </c>
-      <c r="B247" t="n">
-        <v>0</v>
-      </c>
-      <c r="C247" t="inlineStr">
+      <c r="B247" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
         <is>
           <t>孕育兽人战士x5</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="n">
+      <c r="A248" s="2" t="n">
         <v>300710013</v>
       </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
-      <c r="C248" t="inlineStr">
+      <c r="B248" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
         <is>
           <t>孕育兽人战士x10</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="n">
+      <c r="A249" s="2" t="n">
         <v>300710021</v>
       </c>
-      <c r="B249" t="n">
-        <v>0</v>
-      </c>
-      <c r="C249" t="inlineStr">
+      <c r="B249" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
         <is>
           <t>孕育兽人弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="n">
+      <c r="A250" s="2" t="n">
         <v>300710022</v>
       </c>
-      <c r="B250" t="n">
-        <v>0</v>
-      </c>
-      <c r="C250" t="inlineStr">
+      <c r="B250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>孕育兽人弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="n">
+      <c r="A251" s="2" t="n">
         <v>300710023</v>
       </c>
-      <c r="B251" t="n">
-        <v>0</v>
-      </c>
-      <c r="C251" t="inlineStr">
+      <c r="B251" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
         <is>
           <t>孕育兽人弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="n">
+      <c r="A252" s="2" t="n">
         <v>300710031</v>
       </c>
-      <c r="B252" t="n">
-        <v>0</v>
-      </c>
-      <c r="C252" t="inlineStr">
+      <c r="B252" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>孕育兽人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="n">
+      <c r="A253" s="2" t="n">
         <v>300710032</v>
       </c>
-      <c r="B253" t="n">
-        <v>0</v>
-      </c>
-      <c r="C253" t="inlineStr">
+      <c r="B253" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
         <is>
           <t>孕育兽人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="n">
+      <c r="A254" s="2" t="n">
         <v>300710033</v>
       </c>
-      <c r="B254" t="n">
-        <v>0</v>
-      </c>
-      <c r="C254" t="inlineStr">
+      <c r="B254" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>孕育兽人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="n">
+      <c r="A255" s="2" t="n">
         <v>300710041</v>
       </c>
-      <c r="B255" t="n">
-        <v>0</v>
-      </c>
-      <c r="C255" t="inlineStr">
+      <c r="B255" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
         <is>
           <t>孕育兽人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="n">
+      <c r="A256" s="2" t="n">
         <v>300710042</v>
       </c>
-      <c r="B256" t="n">
-        <v>0</v>
-      </c>
-      <c r="C256" t="inlineStr">
+      <c r="B256" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>孕育兽人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="n">
+      <c r="A257" s="2" t="n">
         <v>300710043</v>
       </c>
-      <c r="B257" t="n">
-        <v>0</v>
-      </c>
-      <c r="C257" t="inlineStr">
+      <c r="B257" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
         <is>
           <t>孕育兽人魔法师（冰）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>100300007</v>
+      </c>
+      <c r="B258" t="n">
+        <v>0</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>是魔王就挑战100勇士出现概率</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C258"/>
+  <dimension ref="A1:C266"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1515,2904 +1515,3008 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式</t>
+          <t>剑与魔法-无尽模式·难度2</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>100310112</v>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级2</t>
+      <c r="A36" t="n">
+        <v>100310103</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>剑与魔法-无尽模式·难度3</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>100310113</v>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级3</t>
+      <c r="A37" t="n">
+        <v>100310104</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>剑与魔法-无尽模式·难度4</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>100310114</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级4</t>
+      <c r="A38" t="n">
+        <v>100310105</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>剑与魔法-无尽模式·难度5</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>100310115</v>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级5</t>
+      <c r="A39" t="n">
+        <v>100310106</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>剑与魔法-无尽模式·难度6</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>100310116</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级6</t>
+      <c r="A40" t="n">
+        <v>100310107</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>剑与魔法-无尽模式·难度7</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
-      <c r="A41" s="2" t="n">
-        <v>100310117</v>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级7</t>
+      <c r="A41" t="n">
+        <v>100310108</v>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>剑与魔法-无尽模式·难度8</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
-      <c r="A42" s="2" t="n">
-        <v>100310118</v>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级8</t>
+      <c r="A42" t="n">
+        <v>100310109</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>剑与魔法-无尽模式·难度9</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
-      <c r="A43" s="2" t="n">
-        <v>100310119</v>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>剑与魔法-等级9</t>
+      <c r="A43" t="n">
+        <v>100310110</v>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>剑与魔法-无尽模式·难度10</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>100310120</v>
+        <v>100310112</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级10</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>100310130</v>
+        <v>100310113</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度1-加快进攻节奏</t>
+          <t>剑与魔法-等级3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>100310131</v>
+        <v>100310114</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度2-加快进攻节奏</t>
+          <t>剑与魔法-等级4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>100310132</v>
+        <v>100310115</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度3-加快进攻节奏</t>
+          <t>剑与魔法-等级5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>100310133</v>
+        <v>100310116</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度4-加快进攻节奏</t>
+          <t>剑与魔法-等级6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>100310134</v>
+        <v>100310117</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度5-加快进攻节奏</t>
+          <t>剑与魔法-等级7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>100310135</v>
+        <v>100310118</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度6-加快进攻节奏</t>
+          <t>剑与魔法-等级8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>100310136</v>
+        <v>100310119</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度7-加快进攻节奏</t>
+          <t>剑与魔法-等级9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>100310137</v>
+        <v>100310120</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度8-加快进攻节奏</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>100310138</v>
+        <v>100310130</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度9-加快进攻节奏</t>
+          <t>剑与魔法-难度1-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>100310139</v>
+        <v>100310131</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度10-加快进攻节奏</t>
+          <t>剑与魔法-难度2-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>100310140</v>
+        <v>100310132</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度1-2倍速游戏</t>
+          <t>剑与魔法-难度3-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>100310141</v>
+        <v>100310133</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度2-2倍速游戏</t>
+          <t>剑与魔法-难度4-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>100310142</v>
+        <v>100310134</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度3-2倍速游戏</t>
+          <t>剑与魔法-难度5-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>100310143</v>
+        <v>100310135</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度4-2倍速游戏</t>
+          <t>剑与魔法-难度6-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>100310144</v>
+        <v>100310136</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度5-2倍速游戏</t>
+          <t>剑与魔法-难度7-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>100310145</v>
+        <v>100310137</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度6-2倍速游戏</t>
+          <t>剑与魔法-难度8-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>100310146</v>
+        <v>100310138</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度7-2倍速游戏</t>
+          <t>剑与魔法-难度9-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>100310147</v>
+        <v>100310139</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度8-2倍速游戏</t>
+          <t>剑与魔法-难度10-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>100310148</v>
+        <v>100310140</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度9-2倍速游戏</t>
+          <t>剑与魔法-难度1-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>100310149</v>
+        <v>100310141</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度10-2倍速游戏</t>
+          <t>剑与魔法-难度2-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>100310201</v>
+        <v>100310142</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>剑与魔法-难度3-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>100310202</v>
+        <v>100310143</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>剑与魔法-难度4-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>100310212</v>
+        <v>100310144</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>剑与魔法-难度5-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>100310220</v>
+        <v>100310145</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>剑与魔法-难度6-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>100310301</v>
+        <v>100310146</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>剑与魔法-难度7-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>100310302</v>
+        <v>100310147</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>剑与魔法-难度8-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>100310312</v>
+        <v>100310148</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>剑与魔法-难度9-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>100310320</v>
+        <v>100310149</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>剑与魔法-难度10-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>100310401</v>
+        <v>100310201</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>100310402</v>
+        <v>100310202</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>100310412</v>
+        <v>100310212</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>100310420</v>
+        <v>100310220</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>100400000</v>
+        <v>100310301</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>100400001</v>
+        <v>100310302</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>100401000</v>
+        <v>100310312</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>100401001</v>
+        <v>100310320</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>100402000</v>
+        <v>100310401</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>100402001</v>
+        <v>100310402</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>100403000</v>
+        <v>100310412</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>100403001</v>
+        <v>100310420</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>100500001</v>
+        <v>100400000</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>开启成就系统</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>100600001</v>
+        <v>100400001</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>开启魔汁机</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>100600002</v>
+        <v>100401000</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>魔汁机投入数量+1</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>200000001</v>
+        <v>100401001</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>200000030</v>
+        <v>100402000</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>200100001</v>
+        <v>100402001</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>200100002</v>
+        <v>100403000</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>200100003</v>
+        <v>100403001</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>200100004</v>
+        <v>100500001</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>开启成就系统</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>200200001</v>
+        <v>100600001</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>开启魔汁机</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>200300001</v>
+        <v>100600002</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔汁机投入数量+1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>200400001</v>
+        <v>200000001</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>200500001</v>
+        <v>200000030</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>深渊馈赠刷新次数</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>200600001</v>
+        <v>200100001</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>空格突进</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>200700001</v>
+        <v>200100002</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>突进冷却</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>200800001</v>
+        <v>200100003</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>魔王自动拾取魔晶</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>200900001</v>
+        <v>200100004</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>每次拾取魔晶+1</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>201000001</v>
+        <v>200200001</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>阵容重命名</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>300100000</v>
+        <v>200300001</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>300100001</v>
+        <v>200400001</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>300100002</v>
+        <v>200500001</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>300100003</v>
+        <v>200600001</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>空格突进</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>300100004</v>
+        <v>200700001</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>300100101</v>
+        <v>200800001</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>魔王自动拾取魔晶</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>300100102</v>
+        <v>200900001</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>每次拾取魔晶+1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>300100201</v>
+        <v>201000001</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>阵容重命名</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300100301</v>
+        <v>300100000</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300110011</v>
+        <v>300100001</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>孕育人类战士x1</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300110012</v>
+        <v>300100002</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>孕育人类战士x5</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300110013</v>
+        <v>300100003</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>孕育人类战士x10</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300110021</v>
+        <v>300100004</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>孕育人类弓箭手x1</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300110022</v>
+        <v>300100101</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>孕育人类弓箭手x5</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300110023</v>
+        <v>300100102</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>孕育人类弓箭手x10</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300110031</v>
+        <v>300100201</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（火）x1</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300110032</v>
+        <v>300100301</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（火）x5</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300110033</v>
+        <v>300110011</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（火）x10</t>
+          <t>孕育人类战士x1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300110041</v>
+        <v>300110012</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（冰）x1</t>
+          <t>孕育人类战士x5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>300110042</v>
+        <v>300110013</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（冰）x5</t>
+          <t>孕育人类战士x10</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>300110043</v>
+        <v>300110021</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（冰）x10</t>
+          <t>孕育人类弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>300200000</v>
+        <v>300110022</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>孕育人类弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>300200001</v>
+        <v>300110023</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>孕育人类弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1" s="3">
       <c r="A126" s="2" t="n">
-        <v>300200002</v>
+        <v>300110031</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>孕育人类魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1" s="3">
       <c r="A127" s="2" t="n">
-        <v>300200003</v>
+        <v>300110032</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>孕育人类魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1" s="3">
       <c r="A128" s="2" t="n">
-        <v>300200004</v>
+        <v>300110033</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>孕育人类魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="129" ht="12" customHeight="1" s="3">
       <c r="A129" s="2" t="n">
-        <v>300200101</v>
+        <v>300110041</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>孕育人类魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="130" ht="12" customHeight="1" s="3">
       <c r="A130" s="2" t="n">
-        <v>300200102</v>
+        <v>300110042</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>孕育人类魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="131" ht="12" customHeight="1" s="3">
       <c r="A131" s="2" t="n">
-        <v>300200201</v>
+        <v>300110043</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育人类魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="132" ht="12" customHeight="1" s="3">
       <c r="A132" s="2" t="n">
-        <v>300200301</v>
+        <v>300200000</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="133" ht="12" customHeight="1" s="3">
       <c r="A133" s="2" t="n">
-        <v>300210011</v>
+        <v>300200001</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅战士x1</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="134" ht="12" customHeight="1" s="3">
       <c r="A134" s="2" t="n">
-        <v>300210012</v>
+        <v>300200002</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅战士x5</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>300210013</v>
+        <v>300200003</v>
       </c>
       <c r="B135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅战士x10</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>300210021</v>
+        <v>300200004</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅投手x1</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>300210022</v>
+        <v>300200101</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅投手x5</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>300210023</v>
+        <v>300200102</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅投手x10</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>300210031</v>
+        <v>300200201</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（火）x1</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>300210032</v>
+        <v>300200301</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（火）x5</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>300210033</v>
+        <v>300210011</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（火）x10</t>
+          <t>孕育骷髅战士x1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>300210041</v>
+        <v>300210012</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（冰）x1</t>
+          <t>孕育骷髅战士x5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>300210042</v>
+        <v>300210013</v>
       </c>
       <c r="B143" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（冰）x5</t>
+          <t>孕育骷髅战士x10</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>300210043</v>
+        <v>300210021</v>
       </c>
       <c r="B144" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（冰）x10</t>
+          <t>孕育骷髅投手x1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>300300000</v>
+        <v>300210022</v>
       </c>
       <c r="B145" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>孕育骷髅投手x5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>300300001</v>
+        <v>300210023</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>孕育骷髅投手x10</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>300300002</v>
+        <v>300210031</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>孕育骷髅魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>300300003</v>
+        <v>300210032</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>孕育骷髅魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>300300004</v>
+        <v>300210033</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>孕育骷髅魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>300300101</v>
+        <v>300210041</v>
       </c>
       <c r="B150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>孕育骷髅魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>300300102</v>
+        <v>300210042</v>
       </c>
       <c r="B151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>孕育骷髅魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>300300201</v>
+        <v>300210043</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育骷髅魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>300300301</v>
+        <v>300300000</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>300310011</v>
+        <v>300300001</v>
       </c>
       <c r="B154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>孕育守护史莱姆x1</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>300310012</v>
+        <v>300300002</v>
       </c>
       <c r="B155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>孕育守护史莱姆x5</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>300310013</v>
+        <v>300300003</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>孕育守护史莱姆x10</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>300310021</v>
+        <v>300300004</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>孕育自爆史莱姆x1</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>300310022</v>
+        <v>300300101</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>孕育自爆史莱姆x5</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>300310023</v>
+        <v>300300102</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>孕育自爆史莱姆x10</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>300310031</v>
+        <v>300300201</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>孕育烂泥史莱姆x1</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>300310032</v>
+        <v>300300301</v>
       </c>
       <c r="B161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>孕育烂泥史莱姆x5</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>300310033</v>
+        <v>300310011</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>孕育烂泥史莱姆x10</t>
+          <t>孕育守护史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>300310041</v>
+        <v>300310012</v>
       </c>
       <c r="B163" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>孕育毒液史莱姆x1</t>
+          <t>孕育守护史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>300310042</v>
+        <v>300310013</v>
       </c>
       <c r="B164" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>孕育毒液史莱姆x5</t>
+          <t>孕育守护史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>300310043</v>
+        <v>300310021</v>
       </c>
       <c r="B165" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>孕育毒液史莱姆x10</t>
+          <t>孕育自爆史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>300400000</v>
+        <v>300310022</v>
       </c>
       <c r="B166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>孕育自爆史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>300400001</v>
+        <v>300310023</v>
       </c>
       <c r="B167" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>孕育自爆史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>300400002</v>
+        <v>300310031</v>
       </c>
       <c r="B168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>孕育烂泥史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>300400003</v>
+        <v>300310032</v>
       </c>
       <c r="B169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>孕育烂泥史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>300400004</v>
+        <v>300310033</v>
       </c>
       <c r="B170" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>孕育烂泥史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>300400005</v>
+        <v>300310041</v>
       </c>
       <c r="B171" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>孕育毒液史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>300400101</v>
+        <v>300310042</v>
       </c>
       <c r="B172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>孕育毒液史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>300400102</v>
+        <v>300310043</v>
       </c>
       <c r="B173" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育毒液史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>300400201</v>
+        <v>300400000</v>
       </c>
       <c r="B174" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>300400301</v>
+        <v>300400001</v>
       </c>
       <c r="B175" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>300410011</v>
+        <v>300400002</v>
       </c>
       <c r="B176" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x1</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>300410012</v>
+        <v>300400003</v>
       </c>
       <c r="B177" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x5</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>300410013</v>
+        <v>300400004</v>
       </c>
       <c r="B178" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x10</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>300410021</v>
+        <v>300400005</v>
       </c>
       <c r="B179" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x1</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>300410022</v>
+        <v>300400101</v>
       </c>
       <c r="B180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x5</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>300410023</v>
+        <v>300400102</v>
       </c>
       <c r="B181" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x10</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>300410031</v>
+        <v>300400201</v>
       </c>
       <c r="B182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x1</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>300410032</v>
+        <v>300400301</v>
       </c>
       <c r="B183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x5</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>300410033</v>
+        <v>300410011</v>
       </c>
       <c r="B184" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x10</t>
+          <t>孕育战之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>300410041</v>
+        <v>300410012</v>
       </c>
       <c r="B185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x1</t>
+          <t>孕育战之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>300410042</v>
+        <v>300410013</v>
       </c>
       <c r="B186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x5</t>
+          <t>孕育战之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>300410043</v>
+        <v>300410021</v>
       </c>
       <c r="B187" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x10</t>
+          <t>孕育愈之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>300410051</v>
+        <v>300410022</v>
       </c>
       <c r="B188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x1</t>
+          <t>孕育愈之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>300410052</v>
+        <v>300410023</v>
       </c>
       <c r="B189" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x5</t>
+          <t>孕育愈之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>300410053</v>
+        <v>300410031</v>
       </c>
       <c r="B190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x10</t>
+          <t>孕育惑之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>300500000</v>
+        <v>300410032</v>
       </c>
       <c r="B191" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>孕育惑之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>300500001</v>
+        <v>300410033</v>
       </c>
       <c r="B192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>孕育惑之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>300500002</v>
+        <v>300410041</v>
       </c>
       <c r="B193" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>孕育奥之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>300500003</v>
+        <v>300410042</v>
       </c>
       <c r="B194" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>孕育奥之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>300500004</v>
+        <v>300410043</v>
       </c>
       <c r="B195" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>孕育奥之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>300500101</v>
+        <v>300410051</v>
       </c>
       <c r="B196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>孕育盾之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>300500102</v>
+        <v>300410052</v>
       </c>
       <c r="B197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>孕育盾之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>300500201</v>
+        <v>300410053</v>
       </c>
       <c r="B198" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育盾之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>300500301</v>
+        <v>300500000</v>
       </c>
       <c r="B199" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>300510011</v>
+        <v>300500001</v>
       </c>
       <c r="B200" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x1</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>300510012</v>
+        <v>300500002</v>
       </c>
       <c r="B201" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x5</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>300510013</v>
+        <v>300500003</v>
       </c>
       <c r="B202" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x10</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>300510021</v>
+        <v>300500004</v>
       </c>
       <c r="B203" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x1</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>300510022</v>
+        <v>300500101</v>
       </c>
       <c r="B204" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x5</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>300510023</v>
+        <v>300500102</v>
       </c>
       <c r="B205" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x10</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>300510031</v>
+        <v>300500201</v>
       </c>
       <c r="B206" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x1</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>300510032</v>
+        <v>300500301</v>
       </c>
       <c r="B207" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x5</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>300510033</v>
+        <v>300510011</v>
       </c>
       <c r="B208" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x10</t>
+          <t>孕育牛头人战士x1</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>300510041</v>
+        <v>300510012</v>
       </c>
       <c r="B209" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x1</t>
+          <t>孕育牛头人战士x5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>300510042</v>
+        <v>300510013</v>
       </c>
       <c r="B210" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x5</t>
+          <t>孕育牛头人战士x10</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>300510043</v>
+        <v>300510021</v>
       </c>
       <c r="B211" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x10</t>
+          <t>孕育牛头人投手x1</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>300600000</v>
+        <v>300510022</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>孕育牛头人投手x5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>300600001</v>
+        <v>300510023</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>孕育牛头人投手x10</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>300600002</v>
+        <v>300510031</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>孕育牛头人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>300600003</v>
+        <v>300510032</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>孕育牛头人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>300600004</v>
+        <v>300510033</v>
       </c>
       <c r="B216" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>孕育牛头人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>300600005</v>
+        <v>300510041</v>
       </c>
       <c r="B217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>孕育牛头人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>300600101</v>
+        <v>300510042</v>
       </c>
       <c r="B218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>孕育牛头人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>300600102</v>
+        <v>300510043</v>
       </c>
       <c r="B219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育牛头人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>300600201</v>
+        <v>300600000</v>
       </c>
       <c r="B220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>300600301</v>
+        <v>300600001</v>
       </c>
       <c r="B221" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>300610011</v>
+        <v>300600002</v>
       </c>
       <c r="B222" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x1</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>300610012</v>
+        <v>300600003</v>
       </c>
       <c r="B223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x5</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>300610013</v>
+        <v>300600004</v>
       </c>
       <c r="B224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x10</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>300610021</v>
+        <v>300600005</v>
       </c>
       <c r="B225" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x1</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>300610022</v>
+        <v>300600101</v>
       </c>
       <c r="B226" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x5</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>300610023</v>
+        <v>300600102</v>
       </c>
       <c r="B227" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x10</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>300610031</v>
+        <v>300600201</v>
       </c>
       <c r="B228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x1</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>300610032</v>
+        <v>300600301</v>
       </c>
       <c r="B229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x5</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>300610033</v>
+        <v>300610011</v>
       </c>
       <c r="B230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x10</t>
+          <t>孕育哥布林刺客x1</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>300610041</v>
+        <v>300610012</v>
       </c>
       <c r="B231" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x1</t>
+          <t>孕育哥布林刺客x5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>300610042</v>
+        <v>300610013</v>
       </c>
       <c r="B232" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x5</t>
+          <t>孕育哥布林刺客x10</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>300610043</v>
+        <v>300610021</v>
       </c>
       <c r="B233" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x10</t>
+          <t>孕育哥布林弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>300610051</v>
+        <v>300610022</v>
       </c>
       <c r="B234" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x1</t>
+          <t>孕育哥布林弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>300610052</v>
+        <v>300610023</v>
       </c>
       <c r="B235" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x5</t>
+          <t>孕育哥布林弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>300610053</v>
+        <v>300610031</v>
       </c>
       <c r="B236" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x10</t>
+          <t>孕育哥布林敢死队x1</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>300700000</v>
+        <v>300610032</v>
       </c>
       <c r="B237" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>孕育哥布林敢死队x5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>300700001</v>
+        <v>300610033</v>
       </c>
       <c r="B238" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>孕育哥布林敢死队x10</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>300700002</v>
+        <v>300610041</v>
       </c>
       <c r="B239" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>孕育哥布林魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>300700003</v>
+        <v>300610042</v>
       </c>
       <c r="B240" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>孕育哥布林魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>300700004</v>
+        <v>300610043</v>
       </c>
       <c r="B241" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>孕育哥布林魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>300700101</v>
+        <v>300610051</v>
       </c>
       <c r="B242" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>孕育哥布林魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>300700102</v>
+        <v>300610052</v>
       </c>
       <c r="B243" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育哥布林魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>300700201</v>
+        <v>300610053</v>
       </c>
       <c r="B244" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育哥布林魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>300700301</v>
+        <v>300700000</v>
       </c>
       <c r="B245" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>300710011</v>
+        <v>300700001</v>
       </c>
       <c r="B246" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x1</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>300710012</v>
+        <v>300700002</v>
       </c>
       <c r="B247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x5</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>300710013</v>
+        <v>300700003</v>
       </c>
       <c r="B248" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x10</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>300710021</v>
+        <v>300700004</v>
       </c>
       <c r="B249" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x1</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>300710022</v>
+        <v>300700101</v>
       </c>
       <c r="B250" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x5</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>300710023</v>
+        <v>300700102</v>
       </c>
       <c r="B251" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x10</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>300710031</v>
+        <v>300700201</v>
       </c>
       <c r="B252" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x1</t>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>300710032</v>
+        <v>300700301</v>
       </c>
       <c r="B253" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x5</t>
+          <t>奖励-可获取兽人装备</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>300710033</v>
+        <v>300710011</v>
       </c>
       <c r="B254" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x10</t>
+          <t>孕育兽人战士x1</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>300710041</v>
+        <v>300710012</v>
       </c>
       <c r="B255" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x1</t>
+          <t>孕育兽人战士x5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>300710042</v>
+        <v>300710013</v>
       </c>
       <c r="B256" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x5</t>
+          <t>孕育兽人战士x10</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
+        <v>300710021</v>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人弓箭手x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>300710022</v>
+      </c>
+      <c r="B258" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人弓箭手x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>300710023</v>
+      </c>
+      <c r="B259" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人弓箭手x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>300710031</v>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（火）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>300710032</v>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（火）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>300710033</v>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（火）x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>300710041</v>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（冰）x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>300710042</v>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>孕育兽人魔法师（冰）x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
         <v>300710043</v>
       </c>
-      <c r="B257" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="B265" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
         <is>
           <t>孕育兽人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="n">
+    <row r="266">
+      <c r="A266" s="2" t="n">
         <v>100300007</v>
       </c>
-      <c r="B258" t="n">
-        <v>0</v>
-      </c>
-      <c r="C258" t="inlineStr">
+      <c r="B266" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
         <is>
           <t>是魔王就挑战100勇士出现概率</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C266"/>
+  <dimension ref="A1:C267"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1520,104 +1520,104 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="2" t="n">
         <v>100310103</v>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-无尽模式·难度3</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="2" t="n">
         <v>100310104</v>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-无尽模式·难度4</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="2" t="n">
         <v>100310105</v>
       </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-无尽模式·难度5</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="2" t="n">
         <v>100310106</v>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-无尽模式·难度6</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="2" t="n">
         <v>100310107</v>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-无尽模式·难度7</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
-      <c r="A41" t="n">
+      <c r="A41" s="2" t="n">
         <v>100310108</v>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-无尽模式·难度8</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
-      <c r="A42" t="n">
+      <c r="A42" s="2" t="n">
         <v>100310109</v>
       </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-无尽模式·难度9</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
-      <c r="A43" t="n">
+      <c r="A43" s="2" t="n">
         <v>100310110</v>
       </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-无尽模式·难度10</t>
         </is>
@@ -4519,6 +4519,19 @@
       <c r="C266" s="2" t="inlineStr">
         <is>
           <t>是魔王就挑战100勇士出现概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>100300008</v>
+      </c>
+      <c r="B267" t="n">
+        <v>0</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>无尽模式出现概率</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C267"/>
+  <dimension ref="A1:C268"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -4523,15 +4523,28 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="n">
+      <c r="A267" s="2" t="n">
         <v>100300008</v>
       </c>
-      <c r="B267" t="n">
-        <v>0</v>
-      </c>
-      <c r="C267" t="inlineStr">
+      <c r="B267" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
         <is>
           <t>无尽模式出现概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>100300009</v>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>真勇者挑战(挑战100勇士-BOSS挑战)出现概率</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C268"/>
+  <dimension ref="A1:C269"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1403,3146 +1403,3159 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>100300001</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>传送门可选择世界+1</t>
+      <c r="A27" t="n">
+        <v>100200011</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>挑战100勇士通关获得声望</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>100300002</v>
+        <v>100300001</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-线路数量预览</t>
+          <t>传送门可选择世界+1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>100300003</v>
+        <v>100300002</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-关卡数量预览</t>
+          <t>传送门详情-线路数量预览</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>100300004</v>
+        <v>100300003</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-路径长度预览</t>
+          <t>传送门详情-关卡数量预览</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>100300005</v>
+        <v>100300004</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>传送门详情-奖励预览</t>
+          <t>传送门详情-路径长度预览</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>100300006</v>
+        <v>100300005</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>传送门刷新次数</t>
+          <t>传送门详情-奖励预览</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>100300010</v>
+        <v>100300006</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>传送门可选择世界+10</t>
+          <t>传送门刷新次数</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>100310101</v>
+        <v>100300010</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>世界-剑与魔法</t>
+          <t>传送门可选择世界+10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>100310102</v>
+        <v>100310101</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度2</t>
+          <t>世界-剑与魔法</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>100310103</v>
+        <v>100310102</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度3</t>
+          <t>剑与魔法-无尽模式·难度2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>100310104</v>
+        <v>100310103</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度4</t>
+          <t>剑与魔法-无尽模式·难度3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>100310105</v>
+        <v>100310104</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度5</t>
+          <t>剑与魔法-无尽模式·难度4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>100310106</v>
+        <v>100310105</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度6</t>
+          <t>剑与魔法-无尽模式·难度5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>100310107</v>
+        <v>100310106</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度7</t>
+          <t>剑与魔法-无尽模式·难度6</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="3">
       <c r="A41" s="2" t="n">
-        <v>100310108</v>
+        <v>100310107</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度8</t>
+          <t>剑与魔法-无尽模式·难度7</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="3">
       <c r="A42" s="2" t="n">
-        <v>100310109</v>
+        <v>100310108</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度9</t>
+          <t>剑与魔法-无尽模式·难度8</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="3">
       <c r="A43" s="2" t="n">
-        <v>100310110</v>
+        <v>100310109</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-无尽模式·难度10</t>
+          <t>剑与魔法-无尽模式·难度9</t>
         </is>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="3">
       <c r="A44" s="2" t="n">
-        <v>100310112</v>
+        <v>100310110</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级2</t>
+          <t>剑与魔法-无尽模式·难度10</t>
         </is>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="3">
       <c r="A45" s="2" t="n">
-        <v>100310113</v>
+        <v>100310112</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级3</t>
+          <t>剑与魔法-等级2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>100310114</v>
+        <v>100310113</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级4</t>
+          <t>剑与魔法-等级3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>100310115</v>
+        <v>100310114</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级5</t>
+          <t>剑与魔法-等级4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>100310116</v>
+        <v>100310115</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级6</t>
+          <t>剑与魔法-等级5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>100310117</v>
+        <v>100310116</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级7</t>
+          <t>剑与魔法-等级6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>100310118</v>
+        <v>100310117</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级8</t>
+          <t>剑与魔法-等级7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>100310119</v>
+        <v>100310118</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级9</t>
+          <t>剑与魔法-等级8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>100310120</v>
+        <v>100310119</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-等级10</t>
+          <t>剑与魔法-等级9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>100310130</v>
+        <v>100310120</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度1-加快进攻节奏</t>
+          <t>剑与魔法-等级10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>100310131</v>
+        <v>100310130</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度2-加快进攻节奏</t>
+          <t>剑与魔法-难度1-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>100310132</v>
+        <v>100310131</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度3-加快进攻节奏</t>
+          <t>剑与魔法-难度2-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>100310133</v>
+        <v>100310132</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度4-加快进攻节奏</t>
+          <t>剑与魔法-难度3-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>100310134</v>
+        <v>100310133</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度5-加快进攻节奏</t>
+          <t>剑与魔法-难度4-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>100310135</v>
+        <v>100310134</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度6-加快进攻节奏</t>
+          <t>剑与魔法-难度5-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>100310136</v>
+        <v>100310135</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度7-加快进攻节奏</t>
+          <t>剑与魔法-难度6-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>100310137</v>
+        <v>100310136</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度8-加快进攻节奏</t>
+          <t>剑与魔法-难度7-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>100310138</v>
+        <v>100310137</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度9-加快进攻节奏</t>
+          <t>剑与魔法-难度8-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>100310139</v>
+        <v>100310138</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度10-加快进攻节奏</t>
+          <t>剑与魔法-难度9-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>100310140</v>
+        <v>100310139</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度1-2倍速游戏</t>
+          <t>剑与魔法-难度10-加快进攻节奏</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>100310141</v>
+        <v>100310140</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度2-2倍速游戏</t>
+          <t>剑与魔法-难度1-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>100310142</v>
+        <v>100310141</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度3-2倍速游戏</t>
+          <t>剑与魔法-难度2-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>100310143</v>
+        <v>100310142</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度4-2倍速游戏</t>
+          <t>剑与魔法-难度3-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>100310144</v>
+        <v>100310143</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度5-2倍速游戏</t>
+          <t>剑与魔法-难度4-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>100310145</v>
+        <v>100310144</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度6-2倍速游戏</t>
+          <t>剑与魔法-难度5-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>100310146</v>
+        <v>100310145</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度7-2倍速游戏</t>
+          <t>剑与魔法-难度6-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>100310147</v>
+        <v>100310146</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度8-2倍速游戏</t>
+          <t>剑与魔法-难度7-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>100310148</v>
+        <v>100310147</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度9-2倍速游戏</t>
+          <t>剑与魔法-难度8-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>100310149</v>
+        <v>100310148</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>剑与魔法-难度10-2倍速游戏</t>
+          <t>剑与魔法-难度9-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>100310201</v>
+        <v>100310149</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>世界-虚空魔界</t>
+          <t>剑与魔法-难度10-2倍速游戏</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>100310202</v>
+        <v>100310201</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-无尽模式</t>
+          <t>世界-虚空魔界</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>100310212</v>
+        <v>100310202</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级2</t>
+          <t>虚空魔界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>100310220</v>
+        <v>100310212</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>虚空魔界-等级10</t>
+          <t>虚空魔界-等级2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>100310301</v>
+        <v>100310220</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>世界-刀与剑</t>
+          <t>虚空魔界-等级10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>100310302</v>
+        <v>100310301</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-无尽模式</t>
+          <t>世界-刀与剑</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>100310312</v>
+        <v>100310302</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级2</t>
+          <t>刀与剑-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>100310320</v>
+        <v>100310312</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>刀与剑-等级10</t>
+          <t>刀与剑-等级2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>100310401</v>
+        <v>100310320</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>世界-魔法世界</t>
+          <t>刀与剑-等级10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>100310402</v>
+        <v>100310401</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-无尽模式</t>
+          <t>世界-魔法世界</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>100310412</v>
+        <v>100310402</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级2</t>
+          <t>魔法世界-无尽模式</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>100310420</v>
+        <v>100310412</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>魔法世界-等级10</t>
+          <t>魔法世界-等级2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>100400000</v>
+        <v>100310420</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>开启孕育功能</t>
+          <t>魔法世界-等级10</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>100400001</v>
+        <v>100400000</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>孕育可跳过</t>
+          <t>开启孕育功能</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>100401000</v>
+        <v>100400001</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：R</t>
+          <t>孕育可跳过</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>100401001</v>
+        <v>100401000</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：R 概率+1%</t>
+          <t>解锁孕育稀有度：R</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>100402000</v>
+        <v>100401001</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SR</t>
+          <t>孕育稀有度：R 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>100402001</v>
+        <v>100402000</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SR 概率+1%</t>
+          <t>解锁孕育稀有度：SR</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>100403000</v>
+        <v>100402001</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>解锁孕育稀有度：SSR</t>
+          <t>孕育稀有度：SR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>100403001</v>
+        <v>100403000</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>孕育稀有度：SSR 概率+1%</t>
+          <t>解锁孕育稀有度：SSR</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>100500001</v>
+        <v>100403001</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>开启成就系统</t>
+          <t>孕育稀有度：SSR 概率+1%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>100600001</v>
+        <v>100500001</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>开启魔汁机</t>
+          <t>开启成就系统</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>100600002</v>
+        <v>100600001</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>魔汁机投入数量+1</t>
+          <t>开启魔汁机</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>200000001</v>
+        <v>100600002</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+1</t>
+          <t>魔汁机投入数量+1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>200000030</v>
+        <v>200000001</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>阵容魔物上限+30</t>
+          <t>阵容魔物上限+1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>200100001</v>
+        <v>200000030</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>解锁第二阵容</t>
+          <t>阵容魔物上限+30</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>200100002</v>
+        <v>200100001</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>解锁第三阵容</t>
+          <t>解锁第二阵容</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>200100003</v>
+        <v>200100002</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>解锁第四阵容</t>
+          <t>解锁第三阵容</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>200100004</v>
+        <v>200100003</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>解锁第五阵容</t>
+          <t>解锁第四阵容</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>200200001</v>
+        <v>200100004</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>魔晶掉落存在时长+5秒</t>
+          <t>解锁第五阵容</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>200300001</v>
+        <v>200200001</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力上限+10</t>
+          <t>魔晶掉落存在时长+5秒</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>200400001</v>
+        <v>200300001</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>魔王魔力恢复速度+1/s</t>
+          <t>魔王魔力上限+10</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>200500001</v>
+        <v>200400001</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>深渊馈赠刷新次数</t>
+          <t>魔王魔力恢复速度+1/s</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>200600001</v>
+        <v>200500001</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>空格突进</t>
+          <t>深渊馈赠刷新次数</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>突进冷却</t>
+          <t>空格突进</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>魔王自动拾取魔晶</t>
+          <t>突进冷却</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>每次拾取魔晶+1</t>
+          <t>魔王自动拾取魔晶</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>201000001</v>
+        <v>200900001</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>阵容重命名</t>
+          <t>每次拾取魔晶+1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>300100000</v>
+        <v>201000001</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：人类</t>
+          <t>阵容重命名</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>300100001</v>
+        <v>300100000</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类战士</t>
+          <t>解锁种族：人类</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>300100002</v>
+        <v>300100001</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类弓箭手</t>
+          <t>解锁职业：人类战士</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>300100003</v>
+        <v>300100002</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（火）</t>
+          <t>解锁职业：人类弓箭手</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>300100004</v>
+        <v>300100003</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：人类魔法师（冰）</t>
+          <t>解锁职业：人类魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>300100101</v>
+        <v>300100004</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x5</t>
+          <t>解锁职业：人类魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>300100102</v>
+        <v>300100101</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>孕育人类x10</t>
+          <t>孕育人类x5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>300100201</v>
+        <v>300100102</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>可转生为人类</t>
+          <t>孕育人类x10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>300100301</v>
+        <v>300100201</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取人类装备</t>
+          <t>可转生为人类</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>300110011</v>
+        <v>300100301</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>孕育人类战士x1</t>
+          <t>奖励-可获取人类装备</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>300110012</v>
+        <v>300110011</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>孕育人类战士x5</t>
+          <t>孕育人类战士x1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>300110013</v>
+        <v>300110012</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>孕育人类战士x10</t>
+          <t>孕育人类战士x5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>300110021</v>
+        <v>300110013</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>孕育人类弓箭手x1</t>
+          <t>孕育人类战士x10</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>300110022</v>
+        <v>300110021</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>孕育人类弓箭手x5</t>
+          <t>孕育人类弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>300110023</v>
+        <v>300110022</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>孕育人类弓箭手x10</t>
+          <t>孕育人类弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="126" ht="12" customHeight="1" s="3">
       <c r="A126" s="2" t="n">
-        <v>300110031</v>
+        <v>300110023</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（火）x1</t>
+          <t>孕育人类弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="127" ht="12" customHeight="1" s="3">
       <c r="A127" s="2" t="n">
-        <v>300110032</v>
+        <v>300110031</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（火）x5</t>
+          <t>孕育人类魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="128" ht="12" customHeight="1" s="3">
       <c r="A128" s="2" t="n">
-        <v>300110033</v>
+        <v>300110032</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（火）x10</t>
+          <t>孕育人类魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="129" ht="12" customHeight="1" s="3">
       <c r="A129" s="2" t="n">
-        <v>300110041</v>
+        <v>300110033</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（冰）x1</t>
+          <t>孕育人类魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="130" ht="12" customHeight="1" s="3">
       <c r="A130" s="2" t="n">
-        <v>300110042</v>
+        <v>300110041</v>
       </c>
       <c r="B130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（冰）x5</t>
+          <t>孕育人类魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="131" ht="12" customHeight="1" s="3">
       <c r="A131" s="2" t="n">
-        <v>300110043</v>
+        <v>300110042</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>孕育人类魔法师（冰）x10</t>
+          <t>孕育人类魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="132" ht="12" customHeight="1" s="3">
       <c r="A132" s="2" t="n">
-        <v>300200000</v>
+        <v>300110043</v>
       </c>
       <c r="B132" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：骷髅</t>
+          <t>孕育人类魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="133" ht="12" customHeight="1" s="3">
       <c r="A133" s="2" t="n">
-        <v>300200001</v>
+        <v>300200000</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅战士</t>
+          <t>解锁种族：骷髅</t>
         </is>
       </c>
     </row>
     <row r="134" ht="12" customHeight="1" s="3">
       <c r="A134" s="2" t="n">
-        <v>300200002</v>
+        <v>300200001</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅投手</t>
+          <t>解锁职业：骷髅战士</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>300200003</v>
+        <v>300200002</v>
       </c>
       <c r="B135" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（火）</t>
+          <t>解锁职业：骷髅投手</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>300200004</v>
+        <v>300200003</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：骷髅魔法师（冰）</t>
+          <t>解锁职业：骷髅魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>300200101</v>
+        <v>300200004</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x5</t>
+          <t>解锁职业：骷髅魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>300200102</v>
+        <v>300200101</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅x10</t>
+          <t>孕育骷髅x5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>300200201</v>
+        <v>300200102</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>可转生为骷髅</t>
+          <t>孕育骷髅x10</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>300200301</v>
+        <v>300200201</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取骷髅装备</t>
+          <t>可转生为骷髅</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>300210011</v>
+        <v>300200301</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅战士x1</t>
+          <t>奖励-可获取骷髅装备</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>300210012</v>
+        <v>300210011</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅战士x5</t>
+          <t>孕育骷髅战士x1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>300210013</v>
+        <v>300210012</v>
       </c>
       <c r="B143" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅战士x10</t>
+          <t>孕育骷髅战士x5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>300210021</v>
+        <v>300210013</v>
       </c>
       <c r="B144" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅投手x1</t>
+          <t>孕育骷髅战士x10</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>300210022</v>
+        <v>300210021</v>
       </c>
       <c r="B145" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅投手x5</t>
+          <t>孕育骷髅投手x1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>300210023</v>
+        <v>300210022</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅投手x10</t>
+          <t>孕育骷髅投手x5</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>300210031</v>
+        <v>300210023</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（火）x1</t>
+          <t>孕育骷髅投手x10</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>300210032</v>
+        <v>300210031</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（火）x5</t>
+          <t>孕育骷髅魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>300210033</v>
+        <v>300210032</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（火）x10</t>
+          <t>孕育骷髅魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>300210041</v>
+        <v>300210033</v>
       </c>
       <c r="B150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（冰）x1</t>
+          <t>孕育骷髅魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>300210042</v>
+        <v>300210041</v>
       </c>
       <c r="B151" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（冰）x5</t>
+          <t>孕育骷髅魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>300210043</v>
+        <v>300210042</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>孕育骷髅魔法师（冰）x10</t>
+          <t>孕育骷髅魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>300300000</v>
+        <v>300210043</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：史莱姆</t>
+          <t>孕育骷髅魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>300300001</v>
+        <v>300300000</v>
       </c>
       <c r="B154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：守护史莱姆</t>
+          <t>解锁种族：史莱姆</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>300300002</v>
+        <v>300300001</v>
       </c>
       <c r="B155" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：自爆史莱姆</t>
+          <t>解锁职业：守护史莱姆</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>300300003</v>
+        <v>300300002</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：烂泥史莱姆</t>
+          <t>解锁职业：自爆史莱姆</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>300300004</v>
+        <v>300300003</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：毒液史莱姆</t>
+          <t>解锁职业：烂泥史莱姆</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>300300101</v>
+        <v>300300004</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x5</t>
+          <t>解锁职业：毒液史莱姆</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>300300102</v>
+        <v>300300101</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>孕育史莱姆x10</t>
+          <t>孕育史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>300300201</v>
+        <v>300300102</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>可转生为史莱姆</t>
+          <t>孕育史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>300300301</v>
+        <v>300300201</v>
       </c>
       <c r="B161" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取史莱姆装备</t>
+          <t>可转生为史莱姆</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>300310011</v>
+        <v>300300301</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>孕育守护史莱姆x1</t>
+          <t>奖励-可获取史莱姆装备</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>300310012</v>
+        <v>300310011</v>
       </c>
       <c r="B163" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>孕育守护史莱姆x5</t>
+          <t>孕育守护史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>300310013</v>
+        <v>300310012</v>
       </c>
       <c r="B164" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>孕育守护史莱姆x10</t>
+          <t>孕育守护史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>300310021</v>
+        <v>300310013</v>
       </c>
       <c r="B165" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>孕育自爆史莱姆x1</t>
+          <t>孕育守护史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>300310022</v>
+        <v>300310021</v>
       </c>
       <c r="B166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>孕育自爆史莱姆x5</t>
+          <t>孕育自爆史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>300310023</v>
+        <v>300310022</v>
       </c>
       <c r="B167" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>孕育自爆史莱姆x10</t>
+          <t>孕育自爆史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>300310031</v>
+        <v>300310023</v>
       </c>
       <c r="B168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>孕育烂泥史莱姆x1</t>
+          <t>孕育自爆史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>300310032</v>
+        <v>300310031</v>
       </c>
       <c r="B169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>孕育烂泥史莱姆x5</t>
+          <t>孕育烂泥史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>300310033</v>
+        <v>300310032</v>
       </c>
       <c r="B170" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>孕育烂泥史莱姆x10</t>
+          <t>孕育烂泥史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>300310041</v>
+        <v>300310033</v>
       </c>
       <c r="B171" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>孕育毒液史莱姆x1</t>
+          <t>孕育烂泥史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>300310042</v>
+        <v>300310041</v>
       </c>
       <c r="B172" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>孕育毒液史莱姆x5</t>
+          <t>孕育毒液史莱姆x1</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>300310043</v>
+        <v>300310042</v>
       </c>
       <c r="B173" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>孕育毒液史莱姆x10</t>
+          <t>孕育毒液史莱姆x5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>300400000</v>
+        <v>300310043</v>
       </c>
       <c r="B174" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：魅魔</t>
+          <t>孕育毒液史莱姆x10</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>300400001</v>
+        <v>300400000</v>
       </c>
       <c r="B175" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：战之魅魔</t>
+          <t>解锁种族：魅魔</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>300400002</v>
+        <v>300400001</v>
       </c>
       <c r="B176" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：愈之魅魔</t>
+          <t>解锁职业：战之魅魔</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>300400003</v>
+        <v>300400002</v>
       </c>
       <c r="B177" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：惑之魅魔</t>
+          <t>解锁职业：愈之魅魔</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>300400004</v>
+        <v>300400003</v>
       </c>
       <c r="B178" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：奥之魅魔</t>
+          <t>解锁职业：惑之魅魔</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>300400005</v>
+        <v>300400004</v>
       </c>
       <c r="B179" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>解锁职业：奥之魅魔</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>300400101</v>
+        <v>300400005</v>
       </c>
       <c r="B180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：盾之魅魔</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>300400102</v>
+        <v>300400101</v>
       </c>
       <c r="B181" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>300400201</v>
+        <v>300400102</v>
       </c>
       <c r="B182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>300400301</v>
+        <v>300400201</v>
       </c>
       <c r="B183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>300410011</v>
+        <v>300400301</v>
       </c>
       <c r="B184" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x1</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>300410012</v>
+        <v>300410011</v>
       </c>
       <c r="B185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x5</t>
+          <t>孕育战之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>300410013</v>
+        <v>300410012</v>
       </c>
       <c r="B186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x10</t>
+          <t>孕育战之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>300410021</v>
+        <v>300410013</v>
       </c>
       <c r="B187" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x1</t>
+          <t>孕育战之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>300410022</v>
+        <v>300410021</v>
       </c>
       <c r="B188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x5</t>
+          <t>孕育愈之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>300410023</v>
+        <v>300410022</v>
       </c>
       <c r="B189" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x10</t>
+          <t>孕育愈之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>300410031</v>
+        <v>300410023</v>
       </c>
       <c r="B190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x1</t>
+          <t>孕育愈之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>300410032</v>
+        <v>300410031</v>
       </c>
       <c r="B191" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x5</t>
+          <t>孕育惑之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>300410033</v>
+        <v>300410032</v>
       </c>
       <c r="B192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x10</t>
+          <t>孕育惑之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>300410041</v>
+        <v>300410033</v>
       </c>
       <c r="B193" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x1</t>
+          <t>孕育惑之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>300410042</v>
+        <v>300410041</v>
       </c>
       <c r="B194" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x5</t>
+          <t>孕育奥之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>300410043</v>
+        <v>300410042</v>
       </c>
       <c r="B195" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x10</t>
+          <t>孕育奥之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>300410051</v>
+        <v>300410043</v>
       </c>
       <c r="B196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x1</t>
+          <t>孕育奥之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>300410052</v>
+        <v>300410051</v>
       </c>
       <c r="B197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x5</t>
+          <t>孕育盾之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>300410053</v>
+        <v>300410052</v>
       </c>
       <c r="B198" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x10</t>
+          <t>孕育盾之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>300500000</v>
+        <v>300410053</v>
       </c>
       <c r="B199" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>孕育盾之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>300500001</v>
+        <v>300500000</v>
       </c>
       <c r="B200" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>300500002</v>
+        <v>300500001</v>
       </c>
       <c r="B201" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>300500003</v>
+        <v>300500002</v>
       </c>
       <c r="B202" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>300500004</v>
+        <v>300500003</v>
       </c>
       <c r="B203" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>300500101</v>
+        <v>300500004</v>
       </c>
       <c r="B204" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>300500102</v>
+        <v>300500101</v>
       </c>
       <c r="B205" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>300500201</v>
+        <v>300500102</v>
       </c>
       <c r="B206" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>300500301</v>
+        <v>300500201</v>
       </c>
       <c r="B207" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>300510011</v>
+        <v>300500301</v>
       </c>
       <c r="B208" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x1</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>300510012</v>
+        <v>300510011</v>
       </c>
       <c r="B209" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x5</t>
+          <t>孕育牛头人战士x1</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>300510013</v>
+        <v>300510012</v>
       </c>
       <c r="B210" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x10</t>
+          <t>孕育牛头人战士x5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>300510021</v>
+        <v>300510013</v>
       </c>
       <c r="B211" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x1</t>
+          <t>孕育牛头人战士x10</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>300510022</v>
+        <v>300510021</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x5</t>
+          <t>孕育牛头人投手x1</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>300510023</v>
+        <v>300510022</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x10</t>
+          <t>孕育牛头人投手x5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>300510031</v>
+        <v>300510023</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x1</t>
+          <t>孕育牛头人投手x10</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>300510032</v>
+        <v>300510031</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x5</t>
+          <t>孕育牛头人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>300510033</v>
+        <v>300510032</v>
       </c>
       <c r="B216" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x10</t>
+          <t>孕育牛头人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>300510041</v>
+        <v>300510033</v>
       </c>
       <c r="B217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x1</t>
+          <t>孕育牛头人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>300510042</v>
+        <v>300510041</v>
       </c>
       <c r="B218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x5</t>
+          <t>孕育牛头人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>300510043</v>
+        <v>300510042</v>
       </c>
       <c r="B219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x10</t>
+          <t>孕育牛头人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>300600000</v>
+        <v>300510043</v>
       </c>
       <c r="B220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>孕育牛头人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>300600001</v>
+        <v>300600000</v>
       </c>
       <c r="B221" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>300600002</v>
+        <v>300600001</v>
       </c>
       <c r="B222" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>300600003</v>
+        <v>300600002</v>
       </c>
       <c r="B223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>300600004</v>
+        <v>300600003</v>
       </c>
       <c r="B224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>300600005</v>
+        <v>300600004</v>
       </c>
       <c r="B225" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>300600101</v>
+        <v>300600005</v>
       </c>
       <c r="B226" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>300600102</v>
+        <v>300600101</v>
       </c>
       <c r="B227" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>300600201</v>
+        <v>300600102</v>
       </c>
       <c r="B228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>300600301</v>
+        <v>300600201</v>
       </c>
       <c r="B229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>300610011</v>
+        <v>300600301</v>
       </c>
       <c r="B230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x1</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>300610012</v>
+        <v>300610011</v>
       </c>
       <c r="B231" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x5</t>
+          <t>孕育哥布林刺客x1</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>300610013</v>
+        <v>300610012</v>
       </c>
       <c r="B232" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x10</t>
+          <t>孕育哥布林刺客x5</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>300610021</v>
+        <v>300610013</v>
       </c>
       <c r="B233" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x1</t>
+          <t>孕育哥布林刺客x10</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>300610022</v>
+        <v>300610021</v>
       </c>
       <c r="B234" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x5</t>
+          <t>孕育哥布林弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>300610023</v>
+        <v>300610022</v>
       </c>
       <c r="B235" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x10</t>
+          <t>孕育哥布林弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>300610031</v>
+        <v>300610023</v>
       </c>
       <c r="B236" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x1</t>
+          <t>孕育哥布林弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>300610032</v>
+        <v>300610031</v>
       </c>
       <c r="B237" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x5</t>
+          <t>孕育哥布林敢死队x1</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>300610033</v>
+        <v>300610032</v>
       </c>
       <c r="B238" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x10</t>
+          <t>孕育哥布林敢死队x5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>300610041</v>
+        <v>300610033</v>
       </c>
       <c r="B239" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x1</t>
+          <t>孕育哥布林敢死队x10</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>300610042</v>
+        <v>300610041</v>
       </c>
       <c r="B240" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x5</t>
+          <t>孕育哥布林魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>300610043</v>
+        <v>300610042</v>
       </c>
       <c r="B241" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x10</t>
+          <t>孕育哥布林魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>300610051</v>
+        <v>300610043</v>
       </c>
       <c r="B242" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x1</t>
+          <t>孕育哥布林魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>300610052</v>
+        <v>300610051</v>
       </c>
       <c r="B243" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x5</t>
+          <t>孕育哥布林魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>300610053</v>
+        <v>300610052</v>
       </c>
       <c r="B244" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x10</t>
+          <t>孕育哥布林魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>300700000</v>
+        <v>300610053</v>
       </c>
       <c r="B245" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>孕育哥布林魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>300700001</v>
+        <v>300700000</v>
       </c>
       <c r="B246" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>300700002</v>
+        <v>300700001</v>
       </c>
       <c r="B247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>300700003</v>
+        <v>300700002</v>
       </c>
       <c r="B248" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>300700004</v>
+        <v>300700003</v>
       </c>
       <c r="B249" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>300700101</v>
+        <v>300700004</v>
       </c>
       <c r="B250" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>300700102</v>
+        <v>300700101</v>
       </c>
       <c r="B251" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>300700201</v>
+        <v>300700102</v>
       </c>
       <c r="B252" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>300700301</v>
+        <v>300700201</v>
       </c>
       <c r="B253" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>300710011</v>
+        <v>300700301</v>
       </c>
       <c r="B254" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x1</t>
+          <t>奖励-可获取兽人装备</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>300710012</v>
+        <v>300710011</v>
       </c>
       <c r="B255" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x5</t>
+          <t>孕育兽人战士x1</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>300710013</v>
+        <v>300710012</v>
       </c>
       <c r="B256" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x10</t>
+          <t>孕育兽人战士x5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>300710021</v>
+        <v>300710013</v>
       </c>
       <c r="B257" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x1</t>
+          <t>孕育兽人战士x10</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>300710022</v>
+        <v>300710021</v>
       </c>
       <c r="B258" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x5</t>
+          <t>孕育兽人弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>300710023</v>
+        <v>300710022</v>
       </c>
       <c r="B259" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x10</t>
+          <t>孕育兽人弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>300710031</v>
+        <v>300710023</v>
       </c>
       <c r="B260" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x1</t>
+          <t>孕育兽人弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>300710032</v>
+        <v>300710031</v>
       </c>
       <c r="B261" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x5</t>
+          <t>孕育兽人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>300710033</v>
+        <v>300710032</v>
       </c>
       <c r="B262" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x10</t>
+          <t>孕育兽人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>300710041</v>
+        <v>300710033</v>
       </c>
       <c r="B263" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x1</t>
+          <t>孕育兽人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>300710042</v>
+        <v>300710041</v>
       </c>
       <c r="B264" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x5</t>
+          <t>孕育兽人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>300710043</v>
+        <v>300710042</v>
       </c>
       <c r="B265" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x10</t>
+          <t>孕育兽人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>100300007</v>
+        <v>300710043</v>
       </c>
       <c r="B266" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>是魔王就挑战100勇士出现概率</t>
+          <t>孕育兽人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>100300008</v>
+        <v>100300007</v>
       </c>
       <c r="B267" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>无尽模式出现概率</t>
+          <t>是魔王就挑战100勇士出现概率</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
+        <v>100300008</v>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>无尽模式出现概率</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
         <v>100300009</v>
       </c>
-      <c r="B268" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
+      <c r="B269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
         <is>
           <t>真勇者挑战(挑战100勇士-BOSS挑战)出现概率</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C269"/>
+  <dimension ref="A1:C278"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -1403,13 +1403,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="2" t="n">
         <v>100200011</v>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>挑战100勇士通关获得声望</t>
         </is>
@@ -3393,1171 +3393,1288 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>300400005</v>
+        <v>300400101</v>
       </c>
       <c r="B180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：盾之魅魔</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>300400101</v>
+        <v>300400102</v>
       </c>
       <c r="B181" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>300400102</v>
+        <v>300400201</v>
       </c>
       <c r="B182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>可转生为魅魔</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>300400201</v>
+        <v>300400301</v>
       </c>
       <c r="B183" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>可转生为魅魔</t>
+          <t>奖励-可获取魅魔装备</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>300400301</v>
+        <v>300410011</v>
       </c>
       <c r="B184" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取魅魔装备</t>
+          <t>孕育战之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>300410011</v>
+        <v>300410012</v>
       </c>
       <c r="B185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x1</t>
+          <t>孕育战之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>300410012</v>
+        <v>300410013</v>
       </c>
       <c r="B186" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x5</t>
+          <t>孕育战之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>300410013</v>
+        <v>300410021</v>
       </c>
       <c r="B187" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>孕育战之魅魔x10</t>
+          <t>孕育愈之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>300410021</v>
+        <v>300410022</v>
       </c>
       <c r="B188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x1</t>
+          <t>孕育愈之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>300410022</v>
+        <v>300410023</v>
       </c>
       <c r="B189" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x5</t>
+          <t>孕育愈之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>300410023</v>
+        <v>300410031</v>
       </c>
       <c r="B190" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>孕育愈之魅魔x10</t>
+          <t>孕育惑之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>300410031</v>
+        <v>300410032</v>
       </c>
       <c r="B191" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x1</t>
+          <t>孕育惑之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>300410032</v>
+        <v>300410033</v>
       </c>
       <c r="B192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x5</t>
+          <t>孕育惑之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>300410033</v>
+        <v>300410041</v>
       </c>
       <c r="B193" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>孕育惑之魅魔x10</t>
+          <t>孕育奥之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>300410041</v>
+        <v>300410042</v>
       </c>
       <c r="B194" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x1</t>
+          <t>孕育奥之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>300410042</v>
+        <v>300410043</v>
       </c>
       <c r="B195" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x5</t>
+          <t>孕育奥之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>300410043</v>
+        <v>300410051</v>
       </c>
       <c r="B196" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>孕育奥之魅魔x10</t>
+          <t>孕育盾之魅魔x1</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>300410051</v>
+        <v>300410052</v>
       </c>
       <c r="B197" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x1</t>
+          <t>孕育盾之魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>300410052</v>
+        <v>300410053</v>
       </c>
       <c r="B198" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x5</t>
+          <t>孕育盾之魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>300410053</v>
+        <v>300500000</v>
       </c>
       <c r="B199" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>孕育盾之魅魔x10</t>
+          <t>解锁种族：牛头人</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>300500000</v>
+        <v>300500001</v>
       </c>
       <c r="B200" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：牛头人</t>
+          <t>解锁职业：牛头人战士</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>300500001</v>
+        <v>300500002</v>
       </c>
       <c r="B201" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人战士</t>
+          <t>解锁职业：牛头人投手</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>300500002</v>
+        <v>300500003</v>
       </c>
       <c r="B202" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人投手</t>
+          <t>解锁职业：牛头人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>300500003</v>
+        <v>300500004</v>
       </c>
       <c r="B203" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（火）</t>
+          <t>解锁职业：牛头人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>300500004</v>
+        <v>300500101</v>
       </c>
       <c r="B204" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：牛头人魔法师（冰）</t>
+          <t>孕育牛头人x5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>300500101</v>
+        <v>300500102</v>
       </c>
       <c r="B205" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x5</t>
+          <t>孕育牛头人x10</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>300500102</v>
+        <v>300500201</v>
       </c>
       <c r="B206" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人x10</t>
+          <t>可转生为牛头人</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>300500201</v>
+        <v>300500301</v>
       </c>
       <c r="B207" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>可转生为牛头人</t>
+          <t>奖励-可获取牛头人装备</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>300500301</v>
+        <v>300510011</v>
       </c>
       <c r="B208" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取牛头人装备</t>
+          <t>孕育牛头人战士x1</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>300510011</v>
+        <v>300510012</v>
       </c>
       <c r="B209" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x1</t>
+          <t>孕育牛头人战士x5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>300510012</v>
+        <v>300510013</v>
       </c>
       <c r="B210" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x5</t>
+          <t>孕育牛头人战士x10</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>300510013</v>
+        <v>300510021</v>
       </c>
       <c r="B211" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人战士x10</t>
+          <t>孕育牛头人投手x1</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>300510021</v>
+        <v>300510022</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x1</t>
+          <t>孕育牛头人投手x5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>300510022</v>
+        <v>300510023</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x5</t>
+          <t>孕育牛头人投手x10</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>300510023</v>
+        <v>300510031</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人投手x10</t>
+          <t>孕育牛头人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>300510031</v>
+        <v>300510032</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x1</t>
+          <t>孕育牛头人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>300510032</v>
+        <v>300510033</v>
       </c>
       <c r="B216" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x5</t>
+          <t>孕育牛头人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>300510033</v>
+        <v>300510041</v>
       </c>
       <c r="B217" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（火）x10</t>
+          <t>孕育牛头人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>300510041</v>
+        <v>300510042</v>
       </c>
       <c r="B218" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x1</t>
+          <t>孕育牛头人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>300510042</v>
+        <v>300510043</v>
       </c>
       <c r="B219" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x5</t>
+          <t>孕育牛头人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>300510043</v>
+        <v>300600000</v>
       </c>
       <c r="B220" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>孕育牛头人魔法师（冰）x10</t>
+          <t>解锁种族：哥布林</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>300600000</v>
+        <v>300600001</v>
       </c>
       <c r="B221" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：哥布林</t>
+          <t>解锁职业：哥布林刺客</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>300600001</v>
+        <v>300600002</v>
       </c>
       <c r="B222" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林刺客</t>
+          <t>解锁职业：哥布林弓箭手</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>300600002</v>
+        <v>300600003</v>
       </c>
       <c r="B223" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林弓箭手</t>
+          <t>解锁职业：哥布林敢死队</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>300600003</v>
+        <v>300600004</v>
       </c>
       <c r="B224" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林敢死队</t>
+          <t>解锁职业：哥布林魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>300600004</v>
+        <v>300600005</v>
       </c>
       <c r="B225" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（火）</t>
+          <t>解锁职业：哥布林魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>300600005</v>
+        <v>300600101</v>
       </c>
       <c r="B226" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：哥布林魔法师（冰）</t>
+          <t>孕育魅魔x5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>300600101</v>
+        <v>300600102</v>
       </c>
       <c r="B227" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x5</t>
+          <t>孕育魅魔x10</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>300600102</v>
+        <v>300600201</v>
       </c>
       <c r="B228" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>孕育魅魔x10</t>
+          <t>可转生为哥布林</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>300600201</v>
+        <v>300600301</v>
       </c>
       <c r="B229" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>可转生为哥布林</t>
+          <t>奖励-可获取哥布林装备</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>300600301</v>
+        <v>300610011</v>
       </c>
       <c r="B230" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取哥布林装备</t>
+          <t>孕育哥布林刺客x1</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>300610011</v>
+        <v>300610012</v>
       </c>
       <c r="B231" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x1</t>
+          <t>孕育哥布林刺客x5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>300610012</v>
+        <v>300610013</v>
       </c>
       <c r="B232" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x5</t>
+          <t>孕育哥布林刺客x10</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>300610013</v>
+        <v>300610021</v>
       </c>
       <c r="B233" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林刺客x10</t>
+          <t>孕育哥布林弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>300610021</v>
+        <v>300610022</v>
       </c>
       <c r="B234" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x1</t>
+          <t>孕育哥布林弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>300610022</v>
+        <v>300610023</v>
       </c>
       <c r="B235" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x5</t>
+          <t>孕育哥布林弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>300610023</v>
+        <v>300610031</v>
       </c>
       <c r="B236" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林弓箭手x10</t>
+          <t>孕育哥布林敢死队x1</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>300610031</v>
+        <v>300610032</v>
       </c>
       <c r="B237" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x1</t>
+          <t>孕育哥布林敢死队x5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>300610032</v>
+        <v>300610033</v>
       </c>
       <c r="B238" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x5</t>
+          <t>孕育哥布林敢死队x10</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>300610033</v>
+        <v>300610041</v>
       </c>
       <c r="B239" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林敢死队x10</t>
+          <t>孕育哥布林魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>300610041</v>
+        <v>300610042</v>
       </c>
       <c r="B240" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x1</t>
+          <t>孕育哥布林魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>300610042</v>
+        <v>300610043</v>
       </c>
       <c r="B241" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x5</t>
+          <t>孕育哥布林魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>300610043</v>
+        <v>300610051</v>
       </c>
       <c r="B242" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（火）x10</t>
+          <t>孕育哥布林魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>300610051</v>
+        <v>300610052</v>
       </c>
       <c r="B243" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x1</t>
+          <t>孕育哥布林魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>300610052</v>
+        <v>300610053</v>
       </c>
       <c r="B244" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x5</t>
+          <t>孕育哥布林魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>300610053</v>
+        <v>300700000</v>
       </c>
       <c r="B245" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>孕育哥布林魔法师（冰）x10</t>
+          <t>解锁种族：兽人</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>300700000</v>
+        <v>300700001</v>
       </c>
       <c r="B246" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>解锁种族：兽人</t>
+          <t>解锁职业：兽人战士</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>300700001</v>
+        <v>300700002</v>
       </c>
       <c r="B247" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人战士</t>
+          <t>解锁职业：兽人弓箭手</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>300700002</v>
+        <v>300700003</v>
       </c>
       <c r="B248" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人弓箭手</t>
+          <t>解锁职业：兽人魔法师（火）</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>300700003</v>
+        <v>300700004</v>
       </c>
       <c r="B249" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（火）</t>
+          <t>解锁职业：兽人魔法师（冰）</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>300700004</v>
+        <v>300700101</v>
       </c>
       <c r="B250" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>解锁职业：兽人魔法师（冰）</t>
+          <t>孕育兽人x5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>300700101</v>
+        <v>300700102</v>
       </c>
       <c r="B251" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x5</t>
+          <t>孕育兽人x10</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>300700102</v>
+        <v>300700201</v>
       </c>
       <c r="B252" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人x10</t>
+          <t>可转生兽人</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="n">
-        <v>300700201</v>
+        <v>300700301</v>
       </c>
       <c r="B253" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>可转生兽人</t>
+          <t>奖励-可获取兽人装备</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
-        <v>300700301</v>
+        <v>300710011</v>
       </c>
       <c r="B254" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>奖励-可获取兽人装备</t>
+          <t>孕育兽人战士x1</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="n">
-        <v>300710011</v>
+        <v>300710012</v>
       </c>
       <c r="B255" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x1</t>
+          <t>孕育兽人战士x5</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>300710012</v>
+        <v>300710013</v>
       </c>
       <c r="B256" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x5</t>
+          <t>孕育兽人战士x10</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>300710013</v>
+        <v>300710021</v>
       </c>
       <c r="B257" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人战士x10</t>
+          <t>孕育兽人弓箭手x1</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>300710021</v>
+        <v>300710022</v>
       </c>
       <c r="B258" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x1</t>
+          <t>孕育兽人弓箭手x5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>300710022</v>
+        <v>300710023</v>
       </c>
       <c r="B259" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x5</t>
+          <t>孕育兽人弓箭手x10</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>300710023</v>
+        <v>300710031</v>
       </c>
       <c r="B260" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人弓箭手x10</t>
+          <t>孕育兽人魔法师（火）x1</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>300710031</v>
+        <v>300710032</v>
       </c>
       <c r="B261" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x1</t>
+          <t>孕育兽人魔法师（火）x5</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>300710032</v>
+        <v>300710033</v>
       </c>
       <c r="B262" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x5</t>
+          <t>孕育兽人魔法师（火）x10</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="n">
-        <v>300710033</v>
+        <v>300710041</v>
       </c>
       <c r="B263" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（火）x10</t>
+          <t>孕育兽人魔法师（冰）x1</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
-        <v>300710041</v>
+        <v>300710042</v>
       </c>
       <c r="B264" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x1</t>
+          <t>孕育兽人魔法师（冰）x5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="n">
-        <v>300710042</v>
+        <v>300710043</v>
       </c>
       <c r="B265" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x5</t>
+          <t>孕育兽人魔法师（冰）x10</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
-        <v>300710043</v>
+        <v>100300007</v>
       </c>
       <c r="B266" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>孕育兽人魔法师（冰）x10</t>
+          <t>是魔王就挑战100勇士出现概率</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="n">
-        <v>100300007</v>
+        <v>100300008</v>
       </c>
       <c r="B267" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>是魔王就挑战100勇士出现概率</t>
+          <t>无尽模式出现概率</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="n">
-        <v>100300008</v>
+        <v>100300009</v>
       </c>
       <c r="B268" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>无尽模式出现概率</t>
+          <t>真勇者挑战(挑战100勇士-BOSS挑战)出现概率</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="n">
-        <v>100300009</v>
+        <v>100310150</v>
       </c>
       <c r="B269" s="2" t="n">
         <v>0</v>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>真勇者挑战(挑战100勇士-BOSS挑战)出现概率</t>
+          <t>剑与魔法-难度1-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>100310151</v>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度2-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>100310152</v>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度3-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>100310153</v>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度4-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>100310154</v>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度5-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>100310155</v>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度6-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>100310156</v>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度7-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>100310157</v>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度8-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>100310158</v>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度9-0倍速游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>100310159</v>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>剑与魔法-难度10-0倍速游戏</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C278"/>
+  <dimension ref="A1:C287"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -4678,6 +4678,123 @@
         </is>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>100310160</v>
+      </c>
+      <c r="B279" t="n">
+        <v>0</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度2</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>100310161</v>
+      </c>
+      <c r="B280" t="n">
+        <v>0</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度3</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>100310162</v>
+      </c>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度4</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>100310163</v>
+      </c>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度5</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>100310164</v>
+      </c>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度6</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>100310165</v>
+      </c>
+      <c r="B284" t="n">
+        <v>0</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度7</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>100310166</v>
+      </c>
+      <c r="B285" t="n">
+        <v>0</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度8</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>100310167</v>
+      </c>
+      <c r="B286" t="n">
+        <v>0</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度9</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>100310168</v>
+      </c>
+      <c r="B287" t="n">
+        <v>0</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>剑与魔法-挑战100勇士·难度10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C287"/>
+  <dimension ref="A1:C288"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -4679,119 +4679,132 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="n">
+      <c r="A279" s="2" t="n">
         <v>100310160</v>
       </c>
-      <c r="B279" t="n">
-        <v>0</v>
-      </c>
-      <c r="C279" t="inlineStr">
+      <c r="B279" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度2</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="n">
+      <c r="A280" s="2" t="n">
         <v>100310161</v>
       </c>
-      <c r="B280" t="n">
-        <v>0</v>
-      </c>
-      <c r="C280" t="inlineStr">
+      <c r="B280" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度3</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="n">
+      <c r="A281" s="2" t="n">
         <v>100310162</v>
       </c>
-      <c r="B281" t="n">
-        <v>0</v>
-      </c>
-      <c r="C281" t="inlineStr">
+      <c r="B281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度4</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="n">
+      <c r="A282" s="2" t="n">
         <v>100310163</v>
       </c>
-      <c r="B282" t="n">
-        <v>0</v>
-      </c>
-      <c r="C282" t="inlineStr">
+      <c r="B282" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度5</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="n">
+      <c r="A283" s="2" t="n">
         <v>100310164</v>
       </c>
-      <c r="B283" t="n">
-        <v>0</v>
-      </c>
-      <c r="C283" t="inlineStr">
+      <c r="B283" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度6</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="n">
+      <c r="A284" s="2" t="n">
         <v>100310165</v>
       </c>
-      <c r="B284" t="n">
-        <v>0</v>
-      </c>
-      <c r="C284" t="inlineStr">
+      <c r="B284" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度7</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="n">
+      <c r="A285" s="2" t="n">
         <v>100310166</v>
       </c>
-      <c r="B285" t="n">
-        <v>0</v>
-      </c>
-      <c r="C285" t="inlineStr">
+      <c r="B285" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度8</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="n">
+      <c r="A286" s="2" t="n">
         <v>100310167</v>
       </c>
-      <c r="B286" t="n">
-        <v>0</v>
-      </c>
-      <c r="C286" t="inlineStr">
+      <c r="B286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度9</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="n">
+      <c r="A287" s="2" t="n">
         <v>100310168</v>
       </c>
-      <c r="B287" t="n">
-        <v>0</v>
-      </c>
-      <c r="C287" t="inlineStr">
+      <c r="B287" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
         <is>
           <t>剑与魔法-挑战100勇士·难度10</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>100300011</v>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>传送门详情-来袭魔物预览</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_unlock_info[解锁信息].xlsx
@@ -1044,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C288"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="33.75" customWidth="1" style="3" min="1" max="1"/>
@@ -4796,15 +4796,28 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="n">
+      <c r="A288" s="2" t="n">
         <v>100300011</v>
       </c>
-      <c r="B288" t="n">
-        <v>0</v>
-      </c>
-      <c r="C288" t="inlineStr">
+      <c r="B288" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
         <is>
           <t>传送门详情-来袭魔物预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>100600003</v>
+      </c>
+      <c r="B289" t="n">
+        <v>0</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>魔汁机魔晶附加经验</t>
         </is>
       </c>
     </row>
